--- a/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/6.集成验证需求.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/6.集成验证需求.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>第6章修复校验</t>
+          <t>昇腾 ATLAS A3 900 Superpod*1 CCAE V1R2 版本未确认</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -467,10 +467,58 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260613</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DT 950 产品系列与 HCS V1R2 物认匹配</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ATALAS A3 产品本身移动九天平台 KBS 兼容性测试</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
